--- a/Exam/gymtrackerpro/lib/service/__tests__/it/user-service/createMember-it-form.xlsx
+++ b/Exam/gymtrackerpro/lib/service/__tests__/it/user-service/createMember-it-form.xlsx
@@ -286,7 +286,7 @@
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="11977687" cy="4862512"/>
+    <xdr:ext cx="13701712" cy="4862512"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="1" name="Picture 1">
@@ -771,7 +771,7 @@
   <dimension ref="A1:A24"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="22" width="11" customWidth="1"/>
+    <col min="1" max="25" width="11" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="16" customHeight="1" x14ac:dyDescent="0.25"/>
